--- a/#SaWWorldTourSG_anonymized.xlsx
+++ b/#SaWWorldTourSG_anonymized.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18076,7 +18076,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22172,7 +22172,7 @@
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22264,7 +22264,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22403,7 +22403,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22623,7 +22623,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
